--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-03-2026.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>£13.53</t>
+          <t>£12.71</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>£15.81</t>
+          <t>£15.41</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>£20.18</t>
+          <t>£19.66</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>£20.96</t>
+          <t>£20.41</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>£25.60</t>
+          <t>£24.93</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>£29.50</t>
+          <t>£28.73</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>£28.42</t>
+          <t>Price Not Found</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>£31.96</t>
+          <t>£31.13</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>£36.08</t>
+          <t>£34.86</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>£35.53</t>
+          <t>£34.61</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>£43.62</t>
+          <t>£42.49</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>£44.15</t>
+          <t>£43.00</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>£81.55</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>£53.35</t>
+          <t>£51.97</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£55.57</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>£40.51</t>
+          <t>£41.84</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>£53.89</t>
+          <t>£52.50</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>£9600.0</t>
+          <t>£9750.12</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Error: could not convert string to float: '1,102.88'</t>
+          <t>Error: could not convert string to float: '1,115.00'</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2167,12 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>£32.58</t>
+          <t>£33.62</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>£37.84</t>
+          <t>£36.86</t>
         </is>
       </c>
     </row>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>£36.52</t>
+          <t>£37.68</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>£45.98</t>
+          <t>£44.79</t>
         </is>
       </c>
     </row>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>£39.12</t>
+          <t>£40.37</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>£49.54</t>
+          <t>£48.26</t>
         </is>
       </c>
     </row>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>£40.99</t>
+          <t>£42.13</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>£56.30</t>
+          <t>£54.85</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>£61.78</t>
+          <t>£55.79</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>£60.80</t>
+          <t>£54.99</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>£58.59</t>
+          <t>£53.12</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>£1620.96</t>
+          <t>£1508.96</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>£1872.48</t>
+          <t>£1605.92</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>£1838.4</t>
+          <t>£1790.88</t>
         </is>
       </c>
     </row>
